--- a/e2e/expectedData/sub_Master_Potongan_Expat_Local.xlsx
+++ b/e2e/expectedData/sub_Master_Potongan_Expat_Local.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
   <si>
     <t>DAFTAR POTONGAN GAJI</t>
   </si>
@@ -140,61 +140,22 @@
     <t>30,00</t>
   </si>
   <si>
-    <t>CELIA MARIA REGO DE FATIMA</t>
-  </si>
-  <si>
-    <t>40,00</t>
-  </si>
-  <si>
-    <t>CLAUDIO DA COSTA ALVES</t>
-  </si>
-  <si>
-    <t>600.000,00</t>
-  </si>
-  <si>
-    <t>DIAN EVIYANTI APLUGI</t>
-  </si>
-  <si>
-    <t>800.000,00</t>
-  </si>
-  <si>
-    <t>AHMAD RIYANA SAPUTRA</t>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>1.200.000,00</t>
+  </si>
+  <si>
+    <t>1.400.000,00</t>
   </si>
   <si>
     <t>70,00</t>
   </si>
   <si>
-    <t>RIMBUN SIBURIAN</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>40.000.000,00</t>
-  </si>
-  <si>
-    <t>2.000,00</t>
-  </si>
-  <si>
-    <t>5.000.000,00</t>
-  </si>
-  <si>
-    <t>250,00</t>
-  </si>
-  <si>
-    <t>4.000.000,00</t>
-  </si>
-  <si>
-    <t>3.750,00</t>
-  </si>
-  <si>
-    <t>400,00</t>
-  </si>
-  <si>
-    <t>120,00</t>
-  </si>
-  <si>
-    <t>DILI, 26 AGUSTUS 2026</t>
+    <t>1.780,00</t>
+  </si>
+  <si>
+    <t>DILI, 09 SEPTEMBER 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -305,7 +266,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="571500" cy="333375"/>
@@ -624,7 +585,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="true" style="0"/>
@@ -633,15 +594,15 @@
     <col min="4" max="4" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="11.711" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="8" max="8" width="16.425" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="10.569" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="24.708" bestFit="true" customWidth="true" style="0"/>
     <col min="11" max="11" width="24.708" bestFit="true" customWidth="true" style="0"/>
     <col min="12" max="12" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="6.998" bestFit="true" customWidth="true" style="0"/>
     <col min="14" max="14" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="6.998" bestFit="true" customWidth="true" style="0"/>
     <col min="16" max="16" width="11.711" bestFit="true" customWidth="true" style="0"/>
     <col min="17" max="17" width="26.993" bestFit="true" customWidth="true" style="0"/>
     <col min="18" max="18" width="26.993" bestFit="true" customWidth="true" style="0"/>
@@ -872,371 +833,91 @@
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" s="3">
-        <v>3</v>
-      </c>
-      <c r="B9" s="3">
-        <v>92003</v>
-      </c>
-      <c r="C9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O9" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P9" s="3" t="s">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>35</v>
+      <c r="M9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="N9" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q9" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="3">
-        <v>4</v>
-      </c>
-      <c r="B10" s="3">
-        <v>24005</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q10" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="A10"/>
     </row>
     <row r="11" spans="1:18">
-      <c r="A11" s="3">
-        <v>5</v>
-      </c>
-      <c r="B11" s="3">
-        <v>79001</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L11" s="3" t="s">
+      <c r="A11" t="s">
         <v>46</v>
       </c>
-      <c r="M11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O11" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R11" s="3" t="s">
-        <v>35</v>
-      </c>
+      <c r="E11"/>
+      <c r="G11"/>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12" s="3">
-        <v>6</v>
-      </c>
-      <c r="B12" s="3">
-        <v>95008</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="A12" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O12" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P12" s="3" t="s">
+      <c r="E12"/>
+      <c r="G12" t="s">
         <v>48</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="3">
-        <v>7</v>
-      </c>
-      <c r="B13" s="3">
-        <v>81010</v>
-      </c>
-      <c r="C13" s="3" t="s">
+    </row>
+    <row r="13" spans="1:18" customHeight="1" ht="37.5">
+      <c r="A13"/>
+      <c r="E13"/>
+      <c r="G13"/>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N13" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="O13" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q13" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="R13" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="5" t="s">
+      <c r="E14"/>
+      <c r="G14" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H14" s="4" t="s">
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" t="s">
         <v>51</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="E15"/>
+      <c r="G15" t="s">
         <v>52</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="N14" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="O14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="Q14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="R14" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15"/>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16"/>
-      <c r="G16"/>
-    </row>
-    <row r="17" spans="1:18">
-      <c r="A17" t="s">
-        <v>60</v>
-      </c>
-      <c r="E17"/>
-      <c r="G17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" customHeight="1" ht="37.5">
-      <c r="A18"/>
-      <c r="E18"/>
-      <c r="G18"/>
-    </row>
-    <row r="19" spans="1:18">
-      <c r="A19" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19"/>
-      <c r="G19" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18">
-      <c r="A20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E20"/>
-      <c r="G20" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1259,23 +940,23 @@
     <mergeCell ref="P5:P5"/>
     <mergeCell ref="Q5:Q5"/>
     <mergeCell ref="R5:R5"/>
-    <mergeCell ref="A14:F14"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:R10"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:I14"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:I15"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/e2e/expectedData/sub_Master_Potongan_Expat_Local.xlsx
+++ b/e2e/expectedData/sub_Master_Potongan_Expat_Local.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="84">
   <si>
     <t>DAFTAR POTONGAN GAJI</t>
   </si>
@@ -122,9 +122,18 @@
     <t>ADROALDINO DA SILVA NORONHA TOME</t>
   </si>
   <si>
+    <t>Outsource</t>
+  </si>
+  <si>
+    <t>percentage</t>
+  </si>
+  <si>
     <t>0,00</t>
   </si>
   <si>
+    <t>7,20</t>
+  </si>
+  <si>
     <t>200.000,00</t>
   </si>
   <si>
@@ -137,25 +146,109 @@
     <t>20,00</t>
   </si>
   <si>
+    <t>37,20</t>
+  </si>
+  <si>
+    <t>10,80</t>
+  </si>
+  <si>
+    <t>CELIA MARIA REGO DE FATIMA</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>13,60</t>
+  </si>
+  <si>
+    <t>53,60</t>
+  </si>
+  <si>
+    <t>20,40</t>
+  </si>
+  <si>
+    <t>CLAUDIO DA COSTA ALVES</t>
+  </si>
+  <si>
+    <t>8,40</t>
+  </si>
+  <si>
+    <t>600.000,00</t>
+  </si>
+  <si>
     <t>30,00</t>
   </si>
   <si>
+    <t>58,40</t>
+  </si>
+  <si>
+    <t>12,60</t>
+  </si>
+  <si>
+    <t>DIAN EVIYANTI APLUGI</t>
+  </si>
+  <si>
+    <t>12,00</t>
+  </si>
+  <si>
+    <t>800.000,00</t>
+  </si>
+  <si>
+    <t>40,00</t>
+  </si>
+  <si>
+    <t>72,00</t>
+  </si>
+  <si>
+    <t>18,00</t>
+  </si>
+  <si>
+    <t>AHMAD RIYANA SAPUTRA</t>
+  </si>
+  <si>
+    <t>20,80</t>
+  </si>
+  <si>
+    <t>90,80</t>
+  </si>
+  <si>
+    <t>31,20</t>
+  </si>
+  <si>
+    <t>RIMBUN SIBURIAN</t>
+  </si>
+  <si>
     <t>TOTAL</t>
   </si>
   <si>
-    <t>1.200.000,00</t>
-  </si>
-  <si>
-    <t>1.400.000,00</t>
-  </si>
-  <si>
-    <t>70,00</t>
-  </si>
-  <si>
-    <t>1.780,00</t>
-  </si>
-  <si>
-    <t>DILI, 09 SEPTEMBER 2026</t>
+    <t>40.000.000,00</t>
+  </si>
+  <si>
+    <t>2.000,00</t>
+  </si>
+  <si>
+    <t>262,00</t>
+  </si>
+  <si>
+    <t>5.000.000,00</t>
+  </si>
+  <si>
+    <t>250,00</t>
+  </si>
+  <si>
+    <t>4.000.000,00</t>
+  </si>
+  <si>
+    <t>3.812,00</t>
+  </si>
+  <si>
+    <t>493,00</t>
+  </si>
+  <si>
+    <t>120,00</t>
+  </si>
+  <si>
+    <t>DILI, 10 SEPTEMBER 2026</t>
   </si>
   <si>
     <t>Human Resource</t>
@@ -266,7 +359,7 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="571500" cy="333375"/>
@@ -585,24 +678,24 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R20"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="true" style="0"/>
     <col min="2" max="2" width="6.998" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="38.848" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="11.711" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="12.854" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="10.569" bestFit="true" customWidth="true" style="0"/>
     <col min="8" max="8" width="16.425" bestFit="true" customWidth="true" style="0"/>
     <col min="9" max="9" width="10.569" bestFit="true" customWidth="true" style="0"/>
     <col min="10" max="10" width="24.708" bestFit="true" customWidth="true" style="0"/>
     <col min="11" max="11" width="24.708" bestFit="true" customWidth="true" style="0"/>
     <col min="12" max="12" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="13" max="13" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="13" max="13" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="14" max="14" width="15.282" bestFit="true" customWidth="true" style="0"/>
-    <col min="15" max="15" width="6.998" bestFit="true" customWidth="true" style="0"/>
+    <col min="15" max="15" width="8.141" bestFit="true" customWidth="true" style="0"/>
     <col min="16" max="16" width="11.711" bestFit="true" customWidth="true" style="0"/>
     <col min="17" max="17" width="26.993" bestFit="true" customWidth="true" style="0"/>
     <col min="18" max="18" width="26.993" bestFit="true" customWidth="true" style="0"/>
@@ -787,137 +880,417 @@
         <v>34</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
+      <c r="A9" s="3">
+        <v>3</v>
+      </c>
+      <c r="B9" s="3">
+        <v>92003</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
+      <c r="A10" s="3">
+        <v>4</v>
+      </c>
+      <c r="B10" s="3">
+        <v>24005</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="3">
+        <v>5</v>
+      </c>
+      <c r="B11" s="3">
+        <v>79001</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="3">
+        <v>6</v>
+      </c>
+      <c r="B12" s="3">
+        <v>95008</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="3">
+        <v>7</v>
+      </c>
+      <c r="B13" s="3">
+        <v>81010</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
-      <c r="A9" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="L9" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="M9" s="4" t="s">
+      <c r="L13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="R13" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="N9" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="O9" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q9" s="4" t="s">
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="N14" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="O14" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="R9" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
-      <c r="A10"/>
-    </row>
-    <row r="11" spans="1:18">
-      <c r="A11" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11"/>
-      <c r="G11"/>
-    </row>
-    <row r="12" spans="1:18">
-      <c r="A12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E12"/>
-      <c r="G12" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" customHeight="1" ht="37.5">
-      <c r="A13"/>
-      <c r="E13"/>
-      <c r="G13"/>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="E14"/>
-      <c r="G14" s="1" t="s">
-        <v>50</v>
+      <c r="P14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="Q14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" t="s">
-        <v>51</v>
-      </c>
-      <c r="E15"/>
-      <c r="G15" t="s">
-        <v>52</v>
+      <c r="A15"/>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16"/>
+      <c r="G16"/>
+    </row>
+    <row r="17" spans="1:18">
+      <c r="A17" t="s">
+        <v>78</v>
+      </c>
+      <c r="E17"/>
+      <c r="G17" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" customHeight="1" ht="37.5">
+      <c r="A18"/>
+      <c r="E18"/>
+      <c r="G18"/>
+    </row>
+    <row r="19" spans="1:18">
+      <c r="A19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E19"/>
+      <c r="G19" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18">
+      <c r="A20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E20"/>
+      <c r="G20" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>
@@ -940,23 +1313,23 @@
     <mergeCell ref="P5:P5"/>
     <mergeCell ref="Q5:Q5"/>
     <mergeCell ref="R5:R5"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A10:R10"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:I14"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
   </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
